--- a/output.xlsx
+++ b/output.xlsx
@@ -1,157 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominhquan/Desktop/Cdimex/cào data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67CCE19-A09E-DA4E-9E6A-9FC7B2EB15FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
-    <t>Tên sách</t>
-  </si>
-  <si>
-    <t>NXB</t>
-  </si>
-  <si>
-    <t>Format</t>
-  </si>
-  <si>
-    <t>Khối lượng</t>
-  </si>
-  <si>
-    <t>Dài (Length)</t>
-  </si>
-  <si>
-    <t>Rộng (Width)</t>
-  </si>
-  <si>
-    <t>Cao (Height)</t>
-  </si>
-  <si>
-    <t>image_name</t>
-  </si>
-  <si>
-    <t>description(vi)</t>
-  </si>
-  <si>
-    <t>9780241688243</t>
-  </si>
-  <si>
-    <t>Little Women (Puffin Clothbound Classics)</t>
-  </si>
-  <si>
-    <t>9780241688243.jpg</t>
-  </si>
-  <si>
-    <t>Discover our collectable Puffin Clothbound Classic edition of Little WomenPuffin Clothbound Classics are stunning collectable gift editions of some of the best-loved classics in the world - including this charming edition of Little Women.Christmas won''t be the same this year in the March household, with Father at war and Mother struggling to make ends meet. But even though times are tough, the March sisters'' spirits remain high!''Be comforted, dear soul! There is always light behind the clouds.''Together, through love, heartache, and a ''misplaced'' manuscript, Meg, Jo, Beth, and Amy learn that growing up and into the ''little women'' society expects them to be is going to be much harder than they thought...Collect our Puffin Clothbound Classics:9780241444313 The Little Prince9780241663554 The Jungle Book9780241568811 Charlotte''s Web9780241688243 Little Women9780241688250 Peter Pan9780241688267 The Railway Children9780241688236 Chinese Cinderella9780241411216 Treasure Island9780241411209 The Wizard of Oz9780241655702 Watership Down9780241663578 The Worst Witch9780241663547 David Copperfield9780241663561 The Neverending Story9780241623909 Stig of the Dump9780241623916 The Dark is Rising9780241411162 The Secret Garden9780241411148 Black Beauty9780241411155 Dracula9780241425121 Frankenstein9780241425138 Wuthering Heights9780241425114 Tales from Shakespeare9780241425107 Tales of the Greek Heroes9780241411193 A Christmas Carol9780241621196 Grimms'' Fairy Tales9780241425145 Hans Christian Andersen''s Fairy TalesRead more</t>
-  </si>
-  <si>
-    <t>9780241988268</t>
-  </si>
-  <si>
-    <t>The thursday murder club : the record-breaking sunday times number one bestseller</t>
-  </si>
-  <si>
-    <t>9780241988268.jpg</t>
-  </si>
-  <si>
-    <t>9780241988244</t>
-  </si>
-  <si>
-    <t>The Man Who Died Twice: A Thursday Murder Club Mystery</t>
-  </si>
-  <si>
-    <t>Audible Audiobook</t>
-  </si>
-  <si>
-    <t>9780241988244.jpg</t>
-  </si>
-  <si>
-    <t>The second installment in the beloved andNew York Timesbestselling series from Richard Osman, now streaming on Netflix“It’s taken a mere two books for Richard Osman to vault into the upper leagues of crime writers. . .The Man Who Died Twice. . . dives right into joyous fun."—The New York Times Book ReviewElizabeth, Joyce, Ron and Ibrahim—the Thursday Murder Club—are still riding high off their recent real-life murder case and are looking forward to a bit of peace and quiet at Cooper’s Chase, their posh retirement village.But they are out of luck.An unexpected visitor—an old pal of Elizabeth’s (or perhaps more than just a pal?)—arrives, desperate for her help. He has been accused of stealing diamonds worth millions from the wrong men and he’s seriously on the lam.Then, as night follows day, the first body is found. But not the last. Elizabeth, Joyce, Ron and Ibrahim are up against a ruthless murderer who wouldn’t bat an eyelid at knocking off four septuagenarians. Can our four friends catch the killer before the killer catches them? And if they find the diamonds, too? Well, wouldn’t that be a bonus? You should never put anything beyond the Thursday Murder Club.Richard Osman is back with everyone’s favorite mystery-solving quartet, and the second installment of the Thursday Murder Club series is just as clever and warm as the first—an unputdownable, laugh-out-loud pleasure of a read.Read more</t>
-  </si>
-  <si>
-    <t>9780241992388</t>
-  </si>
-  <si>
-    <t>The Bullet That Missed: A Thursday Murder Club Mystery, Book 3</t>
-  </si>
-  <si>
-    <t>9780241992388.jpg</t>
-  </si>
-  <si>
-    <t>The third installment in the beloved andNew York Timesbestselling series from Richard Osman, now streaming on Netflix“The quartet of aging amateur sleuths…remain wonderful company.” —The New York Times Book ReviewIt is an ordinary Thursday, and things shouldfinallybe returning to normal. Except trouble is never far away where the Thursday Murder Club are concerned. A decade-old cold case—their favorite kind--leads them to a local news legend and a murder with no body and no answers.Then a new foe pays Elizabeth a visit. Her mission? Kill or be killed. Suddenly the cold case has become red hot.While Elizabeth wrestles with her conscience (and a gun), Joyce, Ron, and Ibrahim chase down the clues with help from old friends and new. But can the gang solve the mystery and save Elizabeth before the murderer strikes again?From an upmarket spa to a prison cell complete with espresso machine to a luxury penthouse high in the sky, this third adventure of the Thursday Murder Club is full of the cleverness, intrigue, and irresistible charm that readers have come to expect from Richard Osman’s bestselling series.“The Bullet That Missedhits on every front.”—theWall Street JournalRead more</t>
-  </si>
-  <si>
-    <t>9780241992401</t>
-  </si>
-  <si>
-    <t>The Last Devil to Die: A Thursday Murder Club Mystery, Book 4</t>
-  </si>
-  <si>
-    <t>9780241992401.jpg</t>
-  </si>
-  <si>
-    <t>The fourth installment in the beloved andNew York Timesbestselling series from Richard Osman, now streaming on Netflix“The best Murder Club book yet. . . A poignant complement to both the fair-play mystery plot and the characters’ lively humor.”—TheNew York Times Book ReviewIt's rarely a quiet day for the Thursday Murder Club.Shocking news reaches them—an old friend has been killed, and a dangerous package he was protecting has gone missing.The gang's search leads them into the antiques business, where the tricks of the trade are as old as the objects themselves. As they encounter drug dealers, art forgers, and online fraudsters—as well as heartache close to home—Elizabeth, Joyce, Ron, and Ibrahim have no idea whom to trust.With the body count rising, the clock ticking down, and trouble firmly on their tail, has their luck finally run out?And who will be the last devil to die?Read more</t>
-  </si>
-  <si>
-    <t>9781405930253</t>
-  </si>
-  <si>
-    <t>Anxious People: A Novel</t>
-  </si>
-  <si>
-    <t>9781405930253.jpg</t>
-  </si>
-  <si>
-    <t>An instant #1New York Timesbestseller, the new novel from the author ofA Man Called Oveis a “quirky, big-heartednovel….Wry, wise, and often laugh-out-loud funny, it’s a wholly original story that delivers pure pleasure” (People).Looking at real estate isn’t usually a life-or-death situation, but an apartment open house becomes just that when a failed bank robber bursts in and takes a group of strangers hostage. The captives include a recently retired couple who relentlessly hunt down fixer-uppers to avoid the painful truth that they can’t fix their own marriage. There’s a wealthy bank director who has been too busy to care about anyone else and a young couple who are about to have their first child but can’t seem to agree on anything. Add to the mix an eighty-seven-year-old woman who has lived long enough not to be afraid of someone waving a gun in her face, a flustered but still-ready-to-make-a-deal real estate agent, and a mystery man who has locked himself in the apartment’s only bathroom, and you’ve got the worst group of hostages in the world.Each of them carries a lifetime of grievances, hurts, secrets, and passions that are ready to boil over. None of them is entirely who they appear to be. And all of them—the bank robber included—desperately crave some sort of rescue. As the authorities and the media surround the premises, these reluctant allies will reveal surprising truths about themselves and set in motion a chain of events so unexpected that even they can hardly explain what happens next.Proving once again that Backman is “a master of writing delightful, insightful, soulful, character-driven narratives” (USATODAY),Anxious People“captures the messy essence of being human….It’s clever and affecting, as likely to make you laugh out loud as it is to make you cry” (TheWashington Post). This “endlessly entertaining mood-booster” (Real Simple) is proof that the enduring power of friendship, forgiveness, and hope can save us—even in the most anxious of times.Read more</t>
-  </si>
-  <si>
-    <t>9781405930208</t>
-  </si>
-  <si>
-    <t>Beartown</t>
-  </si>
-  <si>
-    <t>9781405930208.jpg</t>
-  </si>
-  <si>
-    <t>Now an HBO Original Series“You’ll love this engrossing novel.” —PeopleNamed a Best Book of the Year byLibraryReads,BookBrowse, andGoodreadsFrom the #1New York Timesbestselling author ofAnxious People,a dazzling and profound novel about a small town with a big dream—and the price required to make it come true.By the lake in Beartown is an old ice rink, and in that ice rink Kevin, Amat, Benji, and the rest of the town’s junior ice hockey team are about to compete in the national semi-finals—and they actually have a shot at winning. All the hopes and dreams of this place now rest on the shoulders of a handful of teenage boys.Under that heavy burden, the match becomes the catalyst for a violent act that will leave a young girl traumatized and a town in turmoil. Accusations are made and, like ripples on a pond, they travel through all of Beartown.This is a story about a town and a game, but even more about loyalty, commitment, and the responsibilities of friendship; the people we disappoint even though we love them; and the decisions we make every day that come to define us. In this story of a small forest town, Fredrik Backman has found the entire world.Read more</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -170,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -472,158 +408,468 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="38.83203125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ISBN</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tên sách</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>NXB</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Khối lượng</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Dài (Length)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Rộng (Width)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Cao (Height)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>image_url</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>image_name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description(vi)</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>9780241688243</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Little Women (Puffin Clothbound Classics)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Puffin Classics</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Hardcover</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>14.7 ounces</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5.39 inches</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.38 inches</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8.07 inches</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81NZIiOSB4L._SY522_.jpg</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>9780241688243.jpg</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Discover our collectable Puffin Clothbound Classic edition of Little Women Puffin Clothbound Classics are stunning collectable gift editions of some of the best-loved classics in the world - including this charming edition of Little Women.Christmas won''t be the same this year in the March household, with Father at war and Mother struggling to make ends meet. But even though times are tough, the March sisters'' spirits remain high!''Be comforted, dear soul! There is always light behind the clouds.''Together, through love, heartache, and a ''misplaced'' manuscript, Meg, Jo, Beth, and Amy learn that growing up and into the ''little women'' society expects them to be is going to be much harder than they thought...Collect our Puffin Clothbound Classics: 9780241444313 The Little Prince 9780241663554 The Jungle Book 9780241568811 Charlotte''s Web 9780241688243 Little Women 9780241688250 Peter Pan 9780241688267 The Railway Children 9780241688236 Chinese Cinderella  9780241411216 Treasure Island 9780241411209 The Wizard of Oz 9780241655702 Watership Down 9780241663578 The Worst Witch 9780241663547 David Copperfield 9780241663561 The Neverending Story  9780241623909 Stig of the Dump 9780241623916 The Dark is Rising 9780241411162 The Secret Garden 9780241411148 Black Beauty 9780241411155 Dracula 9780241425121 Frankenstein 9780241425138 Wuthering Heights 9780241425114 Tales from Shakespeare 9780241425107 Tales of the Greek Heroes 9780241411193 A Christmas Carol 9780241621196 Grimms'' Fairy Tales 9780241425145 Hans Christian Andersen''s Fairy Tales  Read more</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9780241988268</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The thursday murder club : the record-breaking sunday times number one bestseller</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PENGUIN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Paperback</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9.9 ounces</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5.08 inches</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.98 inches</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7.83 inches</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71zrZf-nvTL._SY522_.jpg</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9780241988268.jpg</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Krimi. In a peaceful retirement village, four unlikely friends meet up once a week to investigate unsolved killings. But when a local property developer shows up dead, 'The Thursday Murder Club' find themselves in the middle of their first live case. The four friends, Elizabeth, Joyce, Ibrahim and Ron, might be octogenarians, but they still have a few tricks up their sleeves. Can our unorthodox but brilliant gang catch the killer, before it's too late?</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9780241988244</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The Man Who Died Twice: A Thursday Murder Club Mystery</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Penguin Audio</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Audible Audiobook</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2.31 pounds</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5.56 inches</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.78 inches</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8.31 inches</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71baH5AgG1L._SX522_.jpg</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9780241988244.jpg</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>The second installment in the beloved and New York Times bestselling series from Richard Osman, now streaming on Netflix“It’s taken a mere two books for Richard Osman to vault into the upper leagues of crime writers. . . The Man Who Died Twice. . . dives right into joyous fun." —The New York Times Book ReviewElizabeth, Joyce, Ron and Ibrahim—the Thursday Murder Club—are still riding high off their recent real-life murder case and are looking forward to a bit of peace and quiet at Cooper’s Chase, their posh retirement village.But they are out of luck.An unexpected visitor—an old pal of Elizabeth’s (or perhaps more than just a pal?)—arrives, desperate for her help. He has been accused of stealing diamonds worth millions from the wrong men and he’s seriously on the lam.Then, as night follows day, the first body is found. But not the last. Elizabeth, Joyce, Ron and Ibrahim are up against a ruthless murderer who wouldn’t bat an eyelid at knocking off four septuagenarians. Can our four friends catch the killer before the killer catches them? And if they find the diamonds, too? Well, wouldn’t that be a bonus? You should never put anything beyond the Thursday Murder Club.Richard Osman is back with everyone’s favorite mystery-solving quartet, and the second installment of the Thursday Murder Club series is just as clever and warm as the first—an unputdownable, laugh-out-loud pleasure of a read.  Read more</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9780241992388</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Bullet That Missed: A Thursday Murder Club Mystery, Book 3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Penguin Audio</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Audible Audiobook</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2.31 pounds</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5.4 inches</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.83 inches</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8.21 inches</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71WrGLuMrNL._SX522_.jpg</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>9780241992388.jpg</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>The third installment in the beloved and New York Times bestselling series from Richard Osman, now streaming on Netflix“The quartet of aging amateur sleuths…remain wonderful company.” —The New York Times Book ReviewIt is an ordinary Thursday, and things should finally be returning to normal. Except trouble is never far away where the Thursday Murder Club are concerned. A decade-old cold case—their favorite kind--leads them to a local news legend and a murder with no body and no answers.Then a new foe pays Elizabeth a visit. Her mission? Kill or be killed. Suddenly the cold case has become red hot.While Elizabeth wrestles with her conscience (and a gun), Joyce, Ron, and Ibrahim chase down the clues with help from old friends and new. But can the gang solve the mystery and save Elizabeth before the murderer strikes again?From an upmarket spa to a prison cell complete with espresso machine to a luxury penthouse high in the sky, this third adventure of the Thursday Murder Club is full of the cleverness, intrigue, and irresistible charm that readers have come to expect from Richard Osman’s bestselling series.“The Bullet That Missed hits on every front.” —the Wall Street Journal  Read more</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" t="s">
-        <v>29</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>9780241992401</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>The Last Devil to Die: A Thursday Murder Club Mystery, Book 4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Penguin Audio</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Audible Audiobook</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10.4 ounces</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5.45 inches</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.88 inches</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8.25 inches</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71KJyGxkJaL._SX522_.jpg</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>9780241992401.jpg</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>The fourth installment in the beloved and New York Times bestselling series from Richard Osman, now streaming on Netflix“The best Murder Club book yet. . . A poignant complement to both the fair-play mystery plot and the characters’ lively humor.”—The New York Times Book ReviewIt's rarely a quiet day for the Thursday Murder Club.Shocking news reaches them—an old friend has been killed, and a dangerous package he was protecting has gone missing.The gang's search leads them into the antiques business, where the tricks of the trade are as old as the objects themselves. As they encounter drug dealers, art forgers, and online fraudsters—as well as heartache close to home—Elizabeth, Joyce, Ron, and Ibrahim have no idea whom to trust.With the body count rising, the clock ticking down, and trouble firmly on their tail, has their luck finally run out?And who will be the last devil to die?  Read more</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" t="s">
-        <v>33</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>9781405930253</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Anxious People: A Novel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Atria Books</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Kindle Edition</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2.31 pounds</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5.31 inches</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.9 inches</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8.25 inches</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/817BGb-V2dL._SY522_.jpg</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9781405930253.jpg</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>An instant #1 New York Times bestseller, the new novel from the author of A Man Called Ove is a “quirky, big-hearted novel….Wry, wise, and often laugh-out-loud funny, it’s a wholly original story that delivers pure pleasure” (People).Looking at real estate isn’t usually a life-or-death situation, but an apartment open house becomes just that when a failed bank robber bursts in and takes a group of strangers hostage. The captives include a recently retired couple who relentlessly hunt down fixer-uppers to avoid the painful truth that they can’t fix their own marriage. There’s a wealthy bank director who has been too busy to care about anyone else and a young couple who are about to have their first child but can’t seem to agree on anything. Add to the mix an eighty-seven-year-old woman who has lived long enough not to be afraid of someone waving a gun in her face, a flustered but still-ready-to-make-a-deal real estate agent, and a mystery man who has locked himself in the apartment’s only bathroom, and you’ve got the worst group of hostages in the world. Each of them carries a lifetime of grievances, hurts, secrets, and passions that are ready to boil over. None of them is entirely who they appear to be. And all of them—the bank robber included—desperately crave some sort of rescue. As the authorities and the media surround the premises, these reluctant allies will reveal surprising truths about themselves and set in motion a chain of events so unexpected that even they can hardly explain what happens next. Proving once again that Backman is “a master of writing delightful, insightful, soulful, character-driven narratives” (USA TODAY), Anxious People “captures the messy essence of being human….It’s clever and affecting, as likely to make you laugh out loud as it is to make you cry” (The Washington Post). This “endlessly entertaining mood-booster” (Real Simple) is proof that the enduring power of friendship, forgiveness, and hope can save us—even in the most anxious of times.  Read more</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" t="s">
-        <v>37</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>9781405930208</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Beartown</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Simon &amp; Schuster Audio</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Audible Audiobook</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2.31 pounds</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5.31 inches</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1.08 inches</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8.25 inches</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/91TDiiXwkeL._SX522_.jpg</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>9781405930208.jpg</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Now an HBO Original Series  “You’ll love this engrossing novel.” —People  Named a Best Book of the Year by LibraryReads, BookBrowse, and Goodreads  From the #1 New York Times bestselling author of Anxious People, a dazzling and profound novel about a small town with a big dream—and the price required to make it come true.By the lake in Beartown is an old ice rink, and in that ice rink Kevin, Amat, Benji, and the rest of the town’s junior ice hockey team are about to compete in the national semi-finals—and they actually have a shot at winning. All the hopes and dreams of this place now rest on the shoulders of a handful of teenage boys.  Under that heavy burden, the match becomes the catalyst for a violent act that will leave a young girl traumatized and a town in turmoil. Accusations are made and, like ripples on a pond, they travel through all of Beartown.  This is a story about a town and a game, but even more about loyalty, commitment, and the responsibilities of friendship; the people we disappoint even though we love them; and the decisions we make every day that come to define us. In this story of a small forest town, Fredrik Backman has found the entire world.  Read more</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output.xlsx
+++ b/output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,74 +476,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9780241688243</t>
+          <t>9781444939453</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Little Women (Puffin Clothbound Classics)</t>
+          <t>Toto Ninja Cat &amp; Great Snake Escape</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Puffin Classics</t>
+          <t>Hodder Children's Books</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hardcover</t>
+          <t>Paperback</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.7 ounces</t>
+          <t>6.2 ounces</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5.39 inches</t>
+          <t>7.76 inches</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.38 inches</t>
+          <t>0.59 inches</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.07 inches</t>
+          <t>5.31 inches</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81NZIiOSB4L._SY522_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/91QwpOHcvVL._SY522_.jpg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9780241688243.jpg</t>
+          <t>9781444939453.jpg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Discover our collectable Puffin Clothbound Classic edition of Little Women Puffin Clothbound Classics are stunning collectable gift editions of some of the best-loved classics in the world - including this charming edition of Little Women.Christmas won''t be the same this year in the March household, with Father at war and Mother struggling to make ends meet. But even though times are tough, the March sisters'' spirits remain high!''Be comforted, dear soul! There is always light behind the clouds.''Together, through love, heartache, and a ''misplaced'' manuscript, Meg, Jo, Beth, and Amy learn that growing up and into the ''little women'' society expects them to be is going to be much harder than they thought...Collect our Puffin Clothbound Classics: 9780241444313 The Little Prince 9780241663554 The Jungle Book 9780241568811 Charlotte''s Web 9780241688243 Little Women 9780241688250 Peter Pan 9780241688267 The Railway Children 9780241688236 Chinese Cinderella  9780241411216 Treasure Island 9780241411209 The Wizard of Oz 9780241655702 Watership Down 9780241663578 The Worst Witch 9780241663547 David Copperfield 9780241663561 The Neverending Story  9780241623909 Stig of the Dump 9780241623916 The Dark is Rising 9780241411162 The Secret Garden 9780241411148 Black Beauty 9780241411155 Dracula 9780241425121 Frankenstein 9780241425138 Wuthering Heights 9780241425114 Tales from Shakespeare 9780241425107 Tales of the Greek Heroes 9780241411193 A Christmas Carol 9780241621196 Grimms'' Fairy Tales 9780241425145 Hans Christian Andersen''s Fairy Tales  Read more</t>
+          <t>Meet Toto: she's no ordinary cat, and she can't wait to have an adventure with you!Toto the cat and her brother Silver live footloose and fancy-free in a townhouse in London. Toto is almost totally blind, and learned to trust her senses from a ninja cat-master who taught her back in Italy where they were born. By day, Toto and Silver seem to be ordinary cats, but by night, they love to have adventures!One evening, news reaches Toto that a king cobra has escaped from London Zoo! Together with help from a very posh cat and two hungry tigers, Toto and Silver must investigate. Can they find the giant snake, before it's too late?  Read more</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9780241988268</t>
+          <t>9780316381251</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The thursday murder club : the record-breaking sunday times number one bestseller</t>
+          <t>How to Safely Use The Ouija Board: An Instruction Manual</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PENGUIN</t>
+          <t>CreateSpace Independent Publishing Platform</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -553,173 +553,173 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.9 ounces</t>
+          <t>1.02 pounds</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5.08 inches</t>
+          <t>6 inches</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.98 inches</t>
+          <t>0.13 inches</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7.83 inches</t>
+          <t>9 inches</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71zrZf-nvTL._SY522_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61owx3ay9HL._SY522_.jpg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9780241988268.jpg</t>
+          <t>9780316381251.jpg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Krimi. In a peaceful retirement village, four unlikely friends meet up once a week to investigate unsolved killings. But when a local property developer shows up dead, 'The Thursday Murder Club' find themselves in the middle of their first live case. The four friends, Elizabeth, Joyce, Ibrahim and Ron, might be octogenarians, but they still have a few tricks up their sleeves. Can our unorthodox but brilliant gang catch the killer, before it's too late?</t>
+          <t>How to Safely Use the Ouija Board comes from over 15 years of sessions. A quick and easy instruction booklet dedicated to the greatest divination tool ever. This book is filled with methods for talking with the dead. A booklet with easy and safe instructions. Featuring an organized team method perfect for a night with friends. Creating energetic, odd and creepy experiences.Daniel's not going to say, "stay away" or "beeeewaaaaare". It's fear created by superstition. This is a rational breakdown with practical methods from a respected figure in a field lacking specialists.About AuthorGhost Guide Daniel has been in the paranormal for over 20 years. As an investigator and Ghost Walks tour guide. For more stories and dark history, listen to the Ghost Guide Daniel Podcast!  Read more</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9780241988244</t>
+          <t>9798339702337</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Man Who Died Twice: A Thursday Murder Club Mystery</t>
+          <t>Events by Kids</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Penguin Audio</t>
+          <t>Independently published</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Audible Audiobook</t>
+          <t>Paperback</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.31 pounds</t>
+          <t>5.6 ounces</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5.56 inches</t>
+          <t>6 inches</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.78 inches</t>
+          <t>0.25 inches</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.31 inches</t>
+          <t>9 inches</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71baH5AgG1L._SX522_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/713xaF-7G5L._SY522_.jpg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9780241988244.jpg</t>
+          <t>9798339702337.jpg</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The second installment in the beloved and New York Times bestselling series from Richard Osman, now streaming on Netflix“It’s taken a mere two books for Richard Osman to vault into the upper leagues of crime writers. . . The Man Who Died Twice. . . dives right into joyous fun." —The New York Times Book ReviewElizabeth, Joyce, Ron and Ibrahim—the Thursday Murder Club—are still riding high off their recent real-life murder case and are looking forward to a bit of peace and quiet at Cooper’s Chase, their posh retirement village.But they are out of luck.An unexpected visitor—an old pal of Elizabeth’s (or perhaps more than just a pal?)—arrives, desperate for her help. He has been accused of stealing diamonds worth millions from the wrong men and he’s seriously on the lam.Then, as night follows day, the first body is found. But not the last. Elizabeth, Joyce, Ron and Ibrahim are up against a ruthless murderer who wouldn’t bat an eyelid at knocking off four septuagenarians. Can our four friends catch the killer before the killer catches them? And if they find the diamonds, too? Well, wouldn’t that be a bonus? You should never put anything beyond the Thursday Murder Club.Richard Osman is back with everyone’s favorite mystery-solving quartet, and the second installment of the Thursday Murder Club series is just as clever and warm as the first—an unputdownable, laugh-out-loud pleasure of a read.  Read more</t>
+          <t>Kid’s events shouldn’t be done by adults—they should be done by kids! "Events by Kids" is an ultimate guide that will empower children to imagine, plan, organize, lead, collaborate, and communicate by planning their own events. This book takes young readers through every step of event planning, from birthday parties to talent shows, making it fun and easy to create unforgettable experiences. With inspiring ideas, hands-on activities, and vibrant examples, this book is perfect for kids who want to take charge and bring their creative visions to life.This book is part of the global project, which includes an online educational course, a series of instructional books, face-to-face activities, and exclusive services for parents. The project’s mission is to empower children by teaching them how to organize and manage their own events, fostering creativity, responsibility, and practical skills that will benefit them throughout their lives. Turn every child into an event-planning superstar with "Events by Kids!”  Read more</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9780241992388</t>
+          <t>9780763692766</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Bullet That Missed: A Thursday Murder Club Mystery, Book 3</t>
+          <t>Get Coding!: Learn HTML, CSS &amp; JavaScript &amp; Build a Website, App &amp; Game</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Penguin Audio</t>
+          <t>Candlewick</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Audible Audiobook</t>
+          <t>Paperback</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.31 pounds</t>
+          <t>1.26 pounds</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5.4 inches</t>
+          <t>7.56 inches</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.83 inches</t>
+          <t>0.59 inches</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.21 inches</t>
+          <t>8.5 inches</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71WrGLuMrNL._SX522_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81olAXS-y1L._SY522_.jpg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9780241992388.jpg</t>
+          <t>9780763692766.jpg</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>The third installment in the beloved and New York Times bestselling series from Richard Osman, now streaming on Netflix“The quartet of aging amateur sleuths…remain wonderful company.” —The New York Times Book ReviewIt is an ordinary Thursday, and things should finally be returning to normal. Except trouble is never far away where the Thursday Murder Club are concerned. A decade-old cold case—their favorite kind--leads them to a local news legend and a murder with no body and no answers.Then a new foe pays Elizabeth a visit. Her mission? Kill or be killed. Suddenly the cold case has become red hot.While Elizabeth wrestles with her conscience (and a gun), Joyce, Ron, and Ibrahim chase down the clues with help from old friends and new. But can the gang solve the mystery and save Elizabeth before the murderer strikes again?From an upmarket spa to a prison cell complete with espresso machine to a luxury penthouse high in the sky, this third adventure of the Thursday Murder Club is full of the cleverness, intrigue, and irresistible charm that readers have come to expect from Richard Osman’s bestselling series.“The Bullet That Missed hits on every front.” —the Wall Street Journal  Read more</t>
+          <t>Learn how to write HTML, CSS, and JavaScript and build your own website, app, and game! An essential guide to computer programming for kids— by kids.Crack open this book and set off on several fun missions — while simultaneously learning the basics of writing code. Want to make a website from scratch? Create an app? Build a game? All the tools are here, laid out in a user-friendly format that leads kids on an imaginary quest to keep a valuable diamond safe from dangerous jewel thieves. Presented by Young Rewired State — an international collective of tech-savvy kids — in easy-to-follow, bite-size chunks, the real-life coding skills taught in this engaging, comprehensive guide may just set young readers on the path to becoming technology stars of the future.  Read more</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9780241992401</t>
+          <t>9781409539117</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Last Devil to Die: A Thursday Murder Club Mystery, Book 4</t>
+          <t>Illustrated Dictionary of Chemistry</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Penguin Audio</t>
+          <t>Usborne</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Audible Audiobook</t>
+          <t>Paperback</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -729,146 +729,260 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5.45 inches</t>
+          <t>6.69 inches</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.88 inches</t>
+          <t>0.39 inches</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.25 inches</t>
+          <t>9.45 inches</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71KJyGxkJaL._SX522_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71EKTOUcfRL._SY522_.jpg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9780241992401.jpg</t>
+          <t>9781409539117.jpg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The fourth installment in the beloved and New York Times bestselling series from Richard Osman, now streaming on Netflix“The best Murder Club book yet. . . A poignant complement to both the fair-play mystery plot and the characters’ lively humor.”—The New York Times Book ReviewIt's rarely a quiet day for the Thursday Murder Club.Shocking news reaches them—an old friend has been killed, and a dangerous package he was protecting has gone missing.The gang's search leads them into the antiques business, where the tricks of the trade are as old as the objects themselves. As they encounter drug dealers, art forgers, and online fraudsters—as well as heartache close to home—Elizabeth, Joyce, Ron, and Ibrahim have no idea whom to trust.With the body count rising, the clock ticking down, and trouble firmly on their tail, has their luck finally run out?And who will be the last devil to die?  Read more</t>
+          <t>This is a new edition of this popular title, which provides a fantastic reference point for students studying for their SATs and GCSE's. It is split into 6 colour coded sections covering all aspects of the curriculum, such as acids and alkalines, reaction rates and the periodic, as well as a general information section which includes essential charts and tables. It is brightly and clearly illustrated. It is internet-linked to further online educational resources through the Usborne Quicklinks website.  Read more</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9781405930253</t>
+          <t>9781803701332</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anxious People: A Novel</t>
+          <t>100 Things to Know About Sport (100 THINGS TO KNOW ABOUT)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Usborne</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kindle Edition</t>
+          <t>Hardcover</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.31 pounds</t>
+          <t>10.4 ounces</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5.31 inches</t>
+          <t>6.93 inches</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.9 inches</t>
+          <t>0.63 inches</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.25 inches</t>
+          <t>9.53 inches</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/817BGb-V2dL._SY522_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/811wM8eqocL._SY522_.jpg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9781405930253.jpg</t>
+          <t>9781803701332.jpg</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>An instant #1 New York Times bestseller, the new novel from the author of A Man Called Ove is a “quirky, big-hearted novel….Wry, wise, and often laugh-out-loud funny, it’s a wholly original story that delivers pure pleasure” (People).Looking at real estate isn’t usually a life-or-death situation, but an apartment open house becomes just that when a failed bank robber bursts in and takes a group of strangers hostage. The captives include a recently retired couple who relentlessly hunt down fixer-uppers to avoid the painful truth that they can’t fix their own marriage. There’s a wealthy bank director who has been too busy to care about anyone else and a young couple who are about to have their first child but can’t seem to agree on anything. Add to the mix an eighty-seven-year-old woman who has lived long enough not to be afraid of someone waving a gun in her face, a flustered but still-ready-to-make-a-deal real estate agent, and a mystery man who has locked himself in the apartment’s only bathroom, and you’ve got the worst group of hostages in the world. Each of them carries a lifetime of grievances, hurts, secrets, and passions that are ready to boil over. None of them is entirely who they appear to be. And all of them—the bank robber included—desperately crave some sort of rescue. As the authorities and the media surround the premises, these reluctant allies will reveal surprising truths about themselves and set in motion a chain of events so unexpected that even they can hardly explain what happens next. Proving once again that Backman is “a master of writing delightful, insightful, soulful, character-driven narratives” (USA TODAY), Anxious People “captures the messy essence of being human….It’s clever and affecting, as likely to make you laugh out loud as it is to make you cry” (The Washington Post). This “endlessly entertaining mood-booster” (Real Simple) is proof that the enduring power of friendship, forgiveness, and hope can save us—even in the most anxious of times.  Read more</t>
+          <t>How do blind athletes tell between silver and gold medals? How did a Finnish architect accidentally invent skateboarding? Why do footballers wear logos on their kit? From equipment and engineering to amazing sporting achievements, find 100 incredible facts in this book, perfect for sharing with family and friends.  Read more</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9781405930208</t>
+          <t>9781536213911</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Beartown</t>
+          <t>Judy Moody: In a Monday Mood</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster Audio</t>
+          <t>Candlewick</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Audible Audiobook</t>
+          <t>Paperback</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.31 pounds</t>
+          <t>4.4 ounces</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5.31 inches</t>
+          <t>5.55 inches</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.08 inches</t>
+          <t>0.39 inches</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.25 inches</t>
+          <t>7.32 inches</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/91TDiiXwkeL._SX522_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81i8O415qXL._SY522_.jpg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9781405930208.jpg</t>
+          <t>9781536213911.jpg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Now an HBO Original Series  “You’ll love this engrossing novel.” —People  Named a Best Book of the Year by LibraryReads, BookBrowse, and Goodreads  From the #1 New York Times bestselling author of Anxious People, a dazzling and profound novel about a small town with a big dream—and the price required to make it come true.By the lake in Beartown is an old ice rink, and in that ice rink Kevin, Amat, Benji, and the rest of the town’s junior ice hockey team are about to compete in the national semi-finals—and they actually have a shot at winning. All the hopes and dreams of this place now rest on the shoulders of a handful of teenage boys.  Under that heavy burden, the match becomes the catalyst for a violent act that will leave a young girl traumatized and a town in turmoil. Accusations are made and, like ripples on a pond, they travel through all of Beartown.  This is a story about a town and a game, but even more about loyalty, commitment, and the responsibilities of friendship; the people we disappoint even though we love them; and the decisions we make every day that come to define us. In this story of a small forest town, Fredrik Backman has found the entire world.  Read more</t>
+          <t>For anyone who has ever had the Sunday night blues, Judy declares that every day can be a holiday if you just find something to celebrate. Happy National Eat Ice Cream for Breakfast Day, anyone?Crumbs! Why can’t every day be Saturday?Judy Moody is Monday-morning mopey. Another week in her same-old seat at her same-old desk in her same-old school. Even worse, there aren’t any days off from school for ages. But when she steps into Class 3T, Judy’s Monday frown turns upside down. Pop! Pop! Pop-pop-pop! Mr. Todd is making Monday special by celebrating Bubble Wrap Appreciation Day (no lie)! This gives Judy an idea that just-might-maybe turn her week around: why not make every day of the week a holiday? But after she and her friends come up with a week’s worth of wacky celebrations, from feeding ninja squirrels to honoring National Sneak Some Zucchini Onto Your Neighbor’s Porch Day, will the weekend be one big letdown?  Read more</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>9780399554520</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Can I Be Your Dog?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Random House Books for Young Readers</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hardcover</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15.2 ounces</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10.39 inches</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.31 inches</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10.24 inches</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81OfJeRL7yL._SY522_.jpg</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9780399554520.jpg</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>The New York Times bestseller featured on THE TODAY SHOW!A heart-tugging dog adoption story told through letters--deeply sincere and almost desperate pleas for a forever home--from the dog, himself!This picture book shares the tale of Arfy, a homeless mutt who lives in a box in an alley. Arfy writes to every person on Butternut Street about what a great pet he'd make. His letters to prospective owners share that he's house broken! He has his own squeaky bone! He can learn to live with cats! But, no one wants him. Won't anyone open their heart--and home--to a lonesome dog? Readers will be happily surprised to learn just who steps up to adopt Arfy. Troy Cummings's hilarious and touching story is a perfect gift for a child wanting a dog, and for pet adoption advocates. It also showcases many different styles of letter writing, making it appealing to parents and teachers looking to teach the lost art of written communication."It's an instant classic in our household." --#1 New York Times bestselling author Sarah J. Maas  Read more</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9780399553578</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Read-Aloud Rhymes for the Very Young</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Knopf Books for Young Readers</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Hardcover</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.4 pounds</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9 inches</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.5 inches</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>11.75 inches</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81WT3CjkHmL._SY522_.jpg</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>9780399553578.jpg</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>First published in 1986 and just as fresh and relevant today, this widely acclaimed, child-friendly poetry anthology is now being reissued with a striking new jacket. In his introduction to this book Jim Trelease, bestselling author of The Read-Aloud Handbook, writes, “No one better recognizes the essence of the child-poetry connection than poet and anthologist Jack Prelutsky. . . . Here are more than 200 little poems to feed little people with little attention spans to help both grow. Marc Brown’s inviting illustrations add a visual dimension to the poems, which further engage young imaginations.” The poems are by 119 of the best-known poets of the 20th century.This book has been selected as a Common Core State Standards Text Exemplar (Grades K-1, Poetry) in Appendix B.  Read more</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominhquan/Desktop/Cdimex/cào data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9C2F6B-C6AC-7245-901C-CA33728EC02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9F1C3F-61F1-0A47-8004-612F807C4780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="262">
   <si>
     <t>ISBN</t>
   </si>
@@ -59,6 +59,753 @@
   </si>
   <si>
     <t>description(vi)</t>
+  </si>
+  <si>
+    <t>9781444939453</t>
+  </si>
+  <si>
+    <t>Toto Ninja Cat &amp; Great Snake Escape</t>
+  </si>
+  <si>
+    <t>Hodder Children's Books</t>
+  </si>
+  <si>
+    <t>Paperback</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>ounces</t>
+  </si>
+  <si>
+    <t>7.76</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>5.31</t>
+  </si>
+  <si>
+    <t>inches</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/91QwpOHcvVL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781444939453.jpg</t>
+  </si>
+  <si>
+    <t>Meet Toto: she's no ordinary cat, and she can't wait to have an adventure with you!Toto the cat and her brother Silver live footloose and fancy-free in a townhouse in London. Toto is almost totally blind, and learned to trust her senses from a ninja cat-master who taught her back in Italy where they were born. By day, Toto and Silver seem to be ordinary cats, but by night, they love to have adventures!One evening, news reaches Toto that a king cobra has escaped from London Zoo! Together with help from a very posh cat and two hungry tigers, Toto and Silver must investigate. Can they find the giant snake, before it's too late?  Read more</t>
+  </si>
+  <si>
+    <t>9780316381251</t>
+  </si>
+  <si>
+    <t>The Iliad: Deluxe Edition Featuring The Achilleid and Original Illustrations (Illustrated)</t>
+  </si>
+  <si>
+    <t>Independently published</t>
+  </si>
+  <si>
+    <t>2.65</t>
+  </si>
+  <si>
+    <t>pounds</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>1.66</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71DynbJRTfL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9780316381251.jpg</t>
+  </si>
+  <si>
+    <t>⚔️Experience the Epic of Achilles Like Never Before⚔️Rage. Honor. Destiny.Step into the legendary world of Ancient Greece with this definitive edition of Homer's masterpiece, The Iliad. Presented in the classic translation by Samuel Butler—now thoughtfully updated to replace his original use of Roman names with their authentic Greek counterparts—this edition invites you to witness the epic clash between mighty Achilles and noble Hector as they battle for glory beneath the walls of Troy. Experience the thunderous intervention of gods, the fierce loyalty of warriors, and the tragic cost of pride in this timeless tale that has captivated readers for millennia.This exclusive volume goes beyond the traditional narrative, featuring the rare inclusion of The Achilleid by Statius. This complementary work offers readers an unprecedented glimpse into the early life of Greece's greatest hero, adding new depths to the legend of Achilles.Enriched with original illustrations and expert commentary, this edition brings the ancient world to vivid life. Whether you're discovering these classics for the first time or returning to beloved tales, this carefully curated collection offers the ultimate journey into the heart of epic poetry.⚔️Why Choose This Edition?✔️ A Deluxe Presentation of Homer's Classic – Dive into the legendary story of Achilles, Hector, and the fall of Troy with a translation that captures the grandeur and intensity of the original epic.✔️ Includes the Rarely Published Achilleid – As a bonus, this volume features The Achilleid by Publius Papinius Statius, translated by J.H. Mozley. This unfinished yet fascinating Latin epic explores Achilles' early years, adding rich depth to his legend.✔️ Exclusive Original Illustrations – This edition is enriched with stunning, hand drawn, original artwork that brings the world of ancient Greece to life, offering a visually immersive reading experience.✔️ Expert Commentary &amp; Thoughtful Insights – Gain a deeper understanding of these timeless works through expertly written commentary, analyzing themes, historical context, and their lasting influence on literature and culture.✔️ Perfect for Collectors and Enthusiasts – Whether you're a literature lover, a student of classical studies, or a collector of fine books, this edition makes a valuable and visually striking addition to any library.⚔️Immerse Yourself in the World of Ancient HeroesFrom Achilles' unrelenting rage to the gods' meddling in mortal affairs, The Iliad captures the essence of heroism and tragedy like no other epic. With the inclusion of The Achilleid, readers gain a rare glimpse into another dimension of Achilles' mythos, making this edition an unparalleled experience for those who love Greek and Roman classics.⚔️Own a Piece of Literary HistoryThis edition of The Iliad is more than just a book—it's an invitation to step into a world of gods, warriors, and legendary battles.Order your copy today and journey into the heart of one of the greatest epics ever told!  Read more</t>
+  </si>
+  <si>
+    <t>9798339702337</t>
+  </si>
+  <si>
+    <t>Events by Kids</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/713xaF-7G5L._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9798339702337.jpg</t>
+  </si>
+  <si>
+    <t>Kid’s events shouldn’t be done by adults—they should be done by kids! "Events by Kids" is an ultimate guide that will empower children to imagine, plan, organize, lead, collaborate, and communicate by planning their own events. This book takes young readers through every step of event planning, from birthday parties to talent shows, making it fun and easy to create unforgettable experiences. With inspiring ideas, hands-on activities, and vibrant examples, this book is perfect for kids who want to take charge and bring their creative visions to life.This book is part of the global project, which includes an online educational course, a series of instructional books, face-to-face activities, and exclusive services for parents. The project’s mission is to empower children by teaching them how to organize and manage their own events, fostering creativity, responsibility, and practical skills that will benefit them throughout their lives. Turn every child into an event-planning superstar with "Events by Kids!”  Read more</t>
+  </si>
+  <si>
+    <t>9780763692766</t>
+  </si>
+  <si>
+    <t>Get Coding!: Learn HTML, CSS &amp; JavaScript &amp; Build a Website, App &amp; Game</t>
+  </si>
+  <si>
+    <t>Candlewick</t>
+  </si>
+  <si>
+    <t>1.26</t>
+  </si>
+  <si>
+    <t>7.56</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81olAXS-y1L._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9780763692766.jpg</t>
+  </si>
+  <si>
+    <t>Learn how to write HTML, CSS, and JavaScript and build your own website, app, and game! An essential guide to computer programming for kids— by kids.Crack open this book and set off on several fun missions — while simultaneously learning the basics of writing code. Want to make a website from scratch? Create an app? Build a game? All the tools are here, laid out in a user-friendly format that leads kids on an imaginary quest to keep a valuable diamond safe from dangerous jewel thieves. Presented by Young Rewired State — an international collective of tech-savvy kids — in easy-to-follow, bite-size chunks, the real-life coding skills taught in this engaging, comprehensive guide may just set young readers on the path to becoming technology stars of the future.  Read more</t>
+  </si>
+  <si>
+    <t>9781409539117</t>
+  </si>
+  <si>
+    <t>Illustrated Dictionary of Chemistry</t>
+  </si>
+  <si>
+    <t>Usborne</t>
+  </si>
+  <si>
+    <t>10.4</t>
+  </si>
+  <si>
+    <t>6.69</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>9.45</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71EKTOUcfRL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781409539117.jpg</t>
+  </si>
+  <si>
+    <t>This is a new edition of this popular title, which provides a fantastic reference point for students studying for their SATs and GCSE's. It is split into 6 colour coded sections covering all aspects of the curriculum, such as acids and alkalines, reaction rates and the periodic, as well as a general information section which includes essential charts and tables. It is brightly and clearly illustrated. It is internet-linked to further online educational resources through the Usborne Quicklinks website.  Read more</t>
+  </si>
+  <si>
+    <t>9781803701332</t>
+  </si>
+  <si>
+    <t>100 Things to Know About Sport (100 THINGS TO KNOW ABOUT)</t>
+  </si>
+  <si>
+    <t>Hardcover</t>
+  </si>
+  <si>
+    <t>6.93</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>9.53</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/811wM8eqocL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781803701332.jpg</t>
+  </si>
+  <si>
+    <t>How do blind athletes tell between silver and gold medals? How did a Finnish architect accidentally invent skateboarding? Why do footballers wear logos on their kit? From equipment and engineering to amazing sporting achievements, find 100 incredible facts in this book, perfect for sharing with family and friends.  Read more</t>
+  </si>
+  <si>
+    <t>9781536213911</t>
+  </si>
+  <si>
+    <t>Judy Moody: In a Monday Mood</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>5.55</t>
+  </si>
+  <si>
+    <t>7.32</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81i8O415qXL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781536213911.jpg</t>
+  </si>
+  <si>
+    <t>For anyone who has ever had the Sunday night blues, Judy declares that every day can be a holiday if you just find something to celebrate. Happy National Eat Ice Cream for Breakfast Day, anyone?Crumbs! Why can’t every day be Saturday?Judy Moody is Monday-morning mopey. Another week in her same-old seat at her same-old desk in her same-old school. Even worse, there aren’t any days off from school for ages. But when she steps into Class 3T, Judy’s Monday frown turns upside down. Pop! Pop! Pop-pop-pop! Mr. Todd is making Monday special by celebrating Bubble Wrap Appreciation Day (no lie)! This gives Judy an idea that just-might-maybe turn her week around: why not make every day of the week a holiday? But after she and her friends come up with a week’s worth of wacky celebrations, from feeding ninja squirrels to honoring National Sneak Some Zucchini Onto Your Neighbor’s Porch Day, will the weekend be one big letdown?  Read more</t>
+  </si>
+  <si>
+    <t>9780399554520</t>
+  </si>
+  <si>
+    <t>Can I Be Your Dog?</t>
+  </si>
+  <si>
+    <t>Random House Books for Young Readers</t>
+  </si>
+  <si>
+    <t>15.2</t>
+  </si>
+  <si>
+    <t>10.39</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>10.24</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81OfJeRL7yL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9780399554520.jpg</t>
+  </si>
+  <si>
+    <t>The New York Times bestseller featured on THE TODAY SHOW!A heart-tugging dog adoption story told through letters--deeply sincere and almost desperate pleas for a forever home--from the dog, himself!This picture book shares the tale of Arfy, a homeless mutt who lives in a box in an alley. Arfy writes to every person on Butternut Street about what a great pet he'd make. His letters to prospective owners share that he's house broken! He has his own squeaky bone! He can learn to live with cats! But, no one wants him. Won't anyone open their heart--and home--to a lonesome dog? Readers will be happily surprised to learn just who steps up to adopt Arfy. Troy Cummings's hilarious and touching story is a perfect gift for a child wanting a dog, and for pet adoption advocates. It also showcases many different styles of letter writing, making it appealing to parents and teachers looking to teach the lost art of written communication."It's an instant classic in our household." --#1 New York Times bestselling author Sarah J. Maas  Read more</t>
+  </si>
+  <si>
+    <t>9780399553578</t>
+  </si>
+  <si>
+    <t>Read-Aloud Rhymes for the Very Young</t>
+  </si>
+  <si>
+    <t>Knopf Books for Young Readers</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>11.75</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81WT3CjkHmL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9780399553578.jpg</t>
+  </si>
+  <si>
+    <t>First published in 1986 and just as fresh and relevant today, this widely acclaimed, child-friendly poetry anthology is now being reissued with a striking new jacket. In his introduction to this book Jim Trelease, bestselling author of The Read-Aloud Handbook, writes, “No one better recognizes the essence of the child-poetry connection than poet and anthologist Jack Prelutsky. . . . Here are more than 200 little poems to feed little people with little attention spans to help both grow. Marc Brown’s inviting illustrations add a visual dimension to the poems, which further engage young imaginations.” The poems are by 119 of the best-known poets of the 20th century.This book has been selected as a Common Core State Standards Text Exemplar (Grades K-1, Poetry) in Appendix B.  Read more</t>
+  </si>
+  <si>
+    <t>9780811827782</t>
+  </si>
+  <si>
+    <t>Enemy Pie : (Reading Rainbow Book, Children’s Book about Kindness, Kids Books about Learning)</t>
+  </si>
+  <si>
+    <t>Chronicle Books</t>
+  </si>
+  <si>
+    <t>10.88</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/7190GKYxsIL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9780811827782.jpg</t>
+  </si>
+  <si>
+    <t>A Reading Rainbow Book! Enemy Pie serves up a sweet lesson as one little boy learns an effective recipe for turning a best enemy into a best friend. "An impressive picture story book about friendship, judgment, and bullying."—Ripple Kindness Project It was the perfect summer. That is, until Jeremy Ross moved into the house down the street and became neighborhood enemy number one. Luckily, Dad had a surefire way to get rid of enemies: Enemy Pie. But part of the secret recipe is spending an entire day playing with the enemy! In this funny yet endearing children's book, filled with charming illustrations, kids learn about dealing with conflict as well as the difficulties, and ultimate rewards, of making new friends. SOCIAL EMOTIONAL LEARNING BOOKS: Enemy Pie is a wonderful addition to books like The Invisible Boy, The Name Jar, and The World Needs Who You Were Made to Be that teach important lessons on kindness, empathy, respect, and friendship. TEACHERS PICK BOOK LIST: Ideal as a read aloud book for elementary schools, and featured on LeVar Burton's Reading Rainbow, this book is recommended by experts for children who are reading independently and transitioning to longer books. POPULAR CHILDREN'S BOOK AUTHOR: Created by Derek Munson who has directly shared his children's stories with over 100,000 kids across the globe.Perfect for:  Parents, teachers, and kids who love Reading Rainbow books  Independent readers in grades 3 – 5  Kids experiencing bullying or conflicts with friends  Readers of books like We Don't Eat Our Classmates, The Choices I Make, and Those Shoes  Read more</t>
+  </si>
+  <si>
+    <t>9780063306608</t>
+  </si>
+  <si>
+    <t>I Am More Than: Empowering Rhyming Verse for Kids of All Ages</t>
+  </si>
+  <si>
+    <t>HarperCollins</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>10.25</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>10.22</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/915PZOKAATL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9780063306608.jpg</t>
+  </si>
+  <si>
+    <t>You can be more than one thing—you can be anything!A follow-up to the #1 New York Times bestselling and critically acclaimed picture book I Promise, this second slam-dunk picture book from NBA champion and cultural icon LeBron James motivates readers to remember they can accomplish their goals when they believe in themselves. Written in fun rhyming verse and illustrated by award-winning and bestselling artist Niña Mata, this book will help little dreamers dream BIG.Perfect for shared reading in and out of the classroom, I Am More Than is also a great gift for graduation, birthdays, and other occasions.  Read more</t>
+  </si>
+  <si>
+    <t>9781250108081</t>
+  </si>
+  <si>
+    <t>Earth! My First 4.54 Billion Years (Our Universe, 1)</t>
+  </si>
+  <si>
+    <t>Henry Holt and Co. (BYR)</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>10.45</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>10.35</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/91bfhl+0VTL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781250108081.jpg</t>
+  </si>
+  <si>
+    <t>"Hi, I’m Earth! But you can call me Planet Awesome." Prepare to learn all about Earth from the point-of-view of Earth herself! In this funny yet informative book, filled to the brim with kid-friendly facts, readers will discover key moments in Earth’s life, from her childhood more than four billion years ago all the way up to present day. Beloved children's book author Stacy McAnulty helps Earth tell her story, and award-winning illustrator David Litchfield brings the words to life. The book includes back matter with even more interesting tidbits.This title has Common Core connections.  Read more</t>
+  </si>
+  <si>
+    <t>9781250108098</t>
+  </si>
+  <si>
+    <t>Ocean! Waves for All (Our Universe, 4)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/91rGU2L5TtL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781250108098.jpg</t>
+  </si>
+  <si>
+    <t>From writer Stacy McAnulty and illustrator David Litchfield, Ocean! Waves for All is a light-hearted nonfiction picture book about the formation and history of the ocean, told from the perspective of the ocean itself.Dude. Ocean is incredible. Atlantic, Pacific, Artic, Indian, Southern―it's all excellent Ocean! Not part of any nation, his waves are for all. And under those waves, man, he holds so many secrets. With characteristic humor and charm, Stacy McAnulty channels the voice of Ocean in this next "autobiography" in the Our Universe series. Rich with kid-friendly facts and beautifully brought to life by David Litchfield, this is an equally charming and irresistible companion to Earth! My First 4.54 Billion Years; Sun! One in a Billion; and Moon! Earth's Best Friend.  Read more</t>
+  </si>
+  <si>
+    <t>9781250199348</t>
+  </si>
+  <si>
+    <t>Moon! Earth's Best Friend (Our Universe, 3)</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>10.3</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81Znn92oHuL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781250199348.jpg</t>
+  </si>
+  <si>
+    <t>From writer Stacy McAnulty and illustrator Stevie Lewis, Moon! Earth's Best Friend is a light-hearted nonfiction picture book about the formation and history of the moon―told from the perspective of the moon itself.Meet Moon! She's more than just a rock―she’s Earth’s rock, her best friend she can always count on. Moon never turns her back on her friend (literally: she's always facing Earth with the same side!). These two will stick together forever. With characteristic humor and charm, Stacy McAnulty channels the voice of Moon in this next celestial "autobiography" in the Our Universe series. Rich with kid-friendly facts and beautifully brought to life by Stevie Lewis, this is an equally charming and irresistible companion to Earth! My First 4.54 Billion Years and Sun! One in a Billion.  Read more</t>
+  </si>
+  <si>
+    <t>9781250813466</t>
+  </si>
+  <si>
+    <t>Pluto!: Not a Planet? Not a Problem! (Our Universe, 7)</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71qKeyibmIL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781250813466.jpg</t>
+  </si>
+  <si>
+    <t>From writer Stacy McAnulty and illustrator Stevie Lewis, Pluto! is a light-hearted nonfiction picture book about the history of the dwarf planet seen through the eyes of Pluto itself. Hot diggity dog! Meet Pluto! The runt of a litter of eight planets. Pluto may not be the biggest or fastest planet to revolve around the Sun, but it has a unique story to tell. From the tale of how it was found by humans to its naming as a dwarf planet, it’s Pluto’s turn to take the spotlight and properly re-introduce itself.With characteristic humor and charm, Stacy McAnulty channels the voice of Pluto in this next celestial "autobiography" in the Our Universe series. Rich with kid-friendly facts and beautifully brought to life by Stevie Lewis, this is an equally charming and irresistible companion to Earth! My First 4.54 Billion Years and Sun! One in a Billion.  Read more</t>
+  </si>
+  <si>
+    <t>9781250199324</t>
+  </si>
+  <si>
+    <t>Sun! One in a Billion (Our Universe, 2)</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/91Dr2wDC-XL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781250199324.jpg</t>
+  </si>
+  <si>
+    <t>From the author of Earth! My First 4.54 Billion Years comes a new picture book about space―this time starring our Sun!Meet Sun: He's a star! And not just any star―he's one in a billion. He lights up our solar system and makes life possible. With characteristic humor and charm, Stacy McAnulty channels the voice of Sun in this next celestial "autobiography." Rich with kid-friendly facts and beautifully illustrated, Sun! One in a Billion is an equally charming and irresistible companion to Earth! My First 4.54 Billion Years.  Read more</t>
+  </si>
+  <si>
+    <t>9781958627051</t>
+  </si>
+  <si>
+    <t>Fruits and Veggies Row by Row: Children Explain How Plants Grow in Their Garden (Multicultural Picture Book - 2nd Edition)</t>
+  </si>
+  <si>
+    <t>Russ Invision Company</t>
+  </si>
+  <si>
+    <t>3.99</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81ADz0JQkmL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781958627051.jpg</t>
+  </si>
+  <si>
+    <t>A group of diverse young children shares their experience growing fruits and vegetables in the garden from seed to sprout to harvest. They clear the land, plant seeds, and tour readers around abundant crops while explaining how different plants grow. This story is a fascinating educational exploration of plant life that celebrates teamwork, cooperation, and the boundless possibilities that bloom in a garden nurtured by youthful enthusiasm. Expand on this book with teachable moments, simple gardening terminology, and opportunities to mimic and move. What a great scientific experience for introducing children to the beneficial process of working the land and reaping the rewards. Teaching children where food comes from effectively gives them control over their diet and promotes healthy eating. Plant something that helps children grow.A garden is where young children can observe natural changes and use their senses to investigate the world. Readers also enjoy searching for hidden insects on the pages. The use of a magnifying glass is recommended.Foundation/Domain:  Life Science32 Pages Size: 8" W x 10" H Available in English and SpanishLyrical rhyming verses and colorful imagery ** This book is printed on demand. Please flip through at least one of the books you receive and contact the publisher directly as soon as possible if you have any quality concerns. **Benefits of Gardening: Practice mapping, designing, and creating a garden.Exposure to a variety of fruits and vegetables and their connection to a rainbow of colors.A socio-emotional experience, working cooperatively toward a positive outcome.Provides a mindful therapeutic, calming effect from outdoor, fresh air activity, disconnected from electronics and the stress of life. (see the Netherlands study)A sensorimotor experience: engages all senses.Gain an understanding of food sources.Encourages the preparation and consumption of fresh produce. Children who grow their own food are more likely to eat fresh fruits and vegetables.Motor skills: engages children and adults in moderate exercise and physical activity: bending, twisting, stretching, lifting, pulling, and reaching.Learn patience and responsibility and gain a sense of confidence.Experience a scientific process that pays off.Develops planning, STEM, and analytical abilities.Introduces biology: the study of living things and their vital processes.Introduces botany: the study of plants, including their structure, properties, and biochemical processes.A chance to study the chemical process of photosynthesis.Provides an opportunity to examine and interact with the environment: weather, temperature, insects, animals, soil, plants, etc.Promotes an appreciation for nature and empathy for the creatures.Explores the limits of natural resources and the importance of using them carefully.Conservation: highlights the importance of taking care of the environment (sustainability).Sunshine on the skin helps the body make Vitamin D! Vitamin D helps our bodies use calcium, keeps our bones strong, and helps us fight diseases.Bulk Orders:  This title is available in bulk directly from the publisher for early childhood and nutrition programs, conferences, non-profit initiatives, licensing, or grants that promote healthy eating, fruits and vegetables, gardening, farm-to-table, STEM initiatives, and anti-obesity. Contact the publisher directly for quotes, orders, and discounted pricing.  Read more</t>
+  </si>
+  <si>
+    <t>9780316353229</t>
+  </si>
+  <si>
+    <t>Big (Caldecott Medal Winner &amp; Coretta Scott King Honor Title)</t>
+  </si>
+  <si>
+    <t>Little, Brown Books for Young Readers</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>9.4</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>10.85</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81D+Tz3p0-L._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9780316353229.jpg</t>
+  </si>
+  <si>
+    <t>Winner of the Caldecott Medal! A Coretta Scott King Award Author and Illustrator Honor book, a National Book Award finalist, and a New York Times bestseller! This deeply moving story shares valuable lessons about fitting in, standing out, and the beauty of joyful acceptance, from an award-winning creator. The first picture book written and illustrated by award-winning creator Vashti Harrison traces a child’s journey to self-love and shows the power of words to both hurt and heal. With spare text and exquisite illustrations, this emotional exploration of being big in a world that prizes small is a tender portrayal of how you can stand out and feel invisible at the same time.  Read more</t>
+  </si>
+  <si>
+    <t>9781465491503</t>
+  </si>
+  <si>
+    <t>Countries of the World: Our World in Pictures</t>
+  </si>
+  <si>
+    <t>DK Children</t>
+  </si>
+  <si>
+    <t>2.34</t>
+  </si>
+  <si>
+    <t>8.74</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>11.18</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/91D6x9hsmTL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781465491503.jpg</t>
+  </si>
+  <si>
+    <t>Packed with more than 1,000 incredible images and full of fascinating facts, this beautiful children’s book takes you on an exciting round-the-globe tour, with a stopover in every nation on every continent!Did you know that Cuba’s national sport is baseball, one of the most popular sports in the US? And that kids in both Japan and Chile have earthquake drills on their school schedule? Find out aboutanything from the spookily vibrant Day of the Dead parade in Mexico and the beautiful springtime cherry blossom displays of Japan, to blueberry-picking in Sweden and India’s space program. Discover the countries of the world – explore their geography, wildlife, traditions, and arts, in this picture-packed children’s book.Every country's profile is full of photos, and each nation has a full-color map detailing its main cities, landscape features, and borders, and exactly where in the world they are, in this engaging encyclopedia for children aged 9-12. Celebrate your child's curiosity as they explore:- Striking and detailed diagrams, drawings and illustrations on every page- A highly visual approach to learning - An ideal combination of colorful diagrams with infographic text boxes- In association with The Smithsonian InstitutionThis captivating kids encyclopedia tackles our weird and wonderful world continent by content, with informative profiles for each of the 196 nations of the world and striking illustrations, photographs and diagrams featured throughout provide an optimum visual learning experience for both children and adults alike, accompanied by an array of fun facts from around the globe!This world encyclopedia includes at-a-glance panels that provide a quick reference to all the stats, making this engaging encyclopedia for kids an ideal combination of colorful diagrams and infographic text boxes with easy-to-read accessible text for readers aged 9-12, yet can be enjoyed by the entire family, making this enthralling children’s encyclopedia a beautiful and educational gift that can be passed down generations.Learn all about the world one picture at a time!If you like Countries of the World, then why not complete the collection? Part of the highly visual Our World In Pictures series, avid readers can dive into the world of dinosaurs with The Dinosaur Book, become a vehicle virtuoso with Cars, Trains, Ships and Planes and explore the incredible animal kingdom with Animal Book.  Read more</t>
+  </si>
+  <si>
+    <t>9781646387465</t>
+  </si>
+  <si>
+    <t>Totally Awesome Logic Puzzles for Kids Ages 4 to 8: Mazes, Spot the Difference, Sudoku, Math Puzzles, Number Patterns, Color by Number, Crack the Code, Counting Games and More</t>
+  </si>
+  <si>
+    <t>Lodi Publishing</t>
+  </si>
+  <si>
+    <t>13.9</t>
+  </si>
+  <si>
+    <t>10.69</t>
+  </si>
+  <si>
+    <t>8.56</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81mP3dG5+OL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781646387465.jpg</t>
+  </si>
+  <si>
+    <t>Your kids will eagerly set aside their screens to enjoy the brain-enhancing challenges in this collection of logic puzzles.Boost Your Child's Brain with Totally Awesome Logic Puzzles for Kids Ages 5 - 8!Your child will enter a vibrant world of logic puzzles and brain teasers with this standout workbook. Specially designed to challenge young minds, this educational activity book is packed with over 80 activities that will both entertain and stimulate your child's brain.Key Features:Diverse Logic Challenges: This book is bursting with over X activities ranging from captivating mazes and spot-the-difference games to Sudoku and math puzzles. Each puzzle is a unique brain workout!Math Games: Delve into the world of math reasoning through games and activities that make learning numbers an engaging experience.Vibrant Colorful Pages: Engaging and brighten art enhances the learning journey.Skill Sharpening: This workbook doesn’t just entertain; it focuses on advancing critical thinking, problem-solving abilities, spatial reasoning, and foundational math skills, ensuring a comprehensive cognitive workout.For the Future Thinkers: Encourage your child to dive deeper into the realms of advanced reasoning and focus. This book is designed to stimulate, challenge, and ensure they're not only having fun but also developing essential skills for the future.Your kids will eagerly set aside their screens to enjoy the brain-enhancing challenges in this collection of logic puzzles.  Read more</t>
+  </si>
+  <si>
+    <t>9781774470381</t>
+  </si>
+  <si>
+    <t>The Girl Who Makes a Million Mistakes: A Growth Mindset Book for Kids to Boost Confidence, Self-Esteem and Resilience (A Million Mistakes Series)</t>
+  </si>
+  <si>
+    <t>Summer and Muu</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61BM0vr93bL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781774470381.jpg</t>
+  </si>
+  <si>
+    <t>Over 120,000 copies sold. A powerful, award-winning growth-mindset book that helps children bounce back from mistakes, build resilience, and believe in themselves. Kids will feel stronger, braver, and ready to chase BIG dreams!Perfect for kids who get frustrated easily or strive to do everything perfect.“This inspiring story teaches kids that it's okay to make mistakes. It turns frustration into perseverance.” — Teacher ReviewThis heartwarming, confidence-boosting story follows Millie, a determined young girl who dreams of becoming a top athlete… but her day keeps falling apart!Tangled hairMissing teethToo much toothpasteGlue everywhereSpilled milkMisspelled bananaAnd a track-and-field race filled with one mistake after another (including landing in a tree!)Millie feels embarrassed, discouraged, and ready to quit.But she discovers the power of learning, problem-solving, mental toughness, and NEVER giving up, no matter how messy things get.With mindful affirmations that help kids regulate big emotions and build inner strength:“I can do this.”“I am strong.”“I am unstoppable.”This motivational book teaches children:That it’s okay to make mistakesHow to learn, try again, and keep goingMental toughness and resiliencePositive self-talk and mindful affirmationsConfidence to chase their goals and dreamsFrom the Readers’ Favorite Silver Award-winning creator of the bestselling Pig in Jeans series, this fun, uplifting story is a must-have for classrooms, libraries, teachers, parents, counselors, and little perfectionists everywhere.Perfect for fans of The Girl Who Never Made Mistakes, The Magical Yet, and This Book Is Perfect.Ideal gift for boys and girls ages 4–7Great for preschool, kindergarten, 1st grade, and 2nd grade.Order your copy of The Girl Who Makes a Million Mistakes today and watch your child grow more confident with every read!  Read more</t>
+  </si>
+  <si>
+    <t>9780877797296</t>
+  </si>
+  <si>
+    <t>Merriam-Webster’s Student Atlas - Features Full-Color Physical, Political, &amp; Thematic Maps</t>
+  </si>
+  <si>
+    <t>Merriam-Webster, Inc.</t>
+  </si>
+  <si>
+    <t>13.6</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/91ef2dQJbRL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9780877797296.jpg</t>
+  </si>
+  <si>
+    <t>Explore the world around you with this engaging collection of maps designed especially for middle schoolers.The latest edition of Merriam-Webster’s Student Atlas has been updated to reflect recent global events and features abundant full-color physical, political, and thematic maps.Discover the world’s landforms and bodies of water, the highest and lowest elevations, and learn more about ocean currents, and wind patterns. Thematic maps cover diverse topics such as continental drift, ocean floor, climate, natural resources, and population density.Features up-to-date statistics and global information. Packed with photographs and easy-to-use charts and graphs and featuring a glossary with brief definitions, this book is the perfect resource for kids interested in exploring the world around them both at home and in the classroom.  Read more</t>
+  </si>
+  <si>
+    <t>9781951056773</t>
+  </si>
+  <si>
+    <t>Ninja Life Hacks Emotions and Feelings 8 Book Box Set (Books 1-8: Angry, Inventor, Positive, Lazy, Helpful, Earth, Grumpy, Kind)</t>
+  </si>
+  <si>
+    <t>Grow Grit Press</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/812nq5Yo+VL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781951056773.jpg</t>
+  </si>
+  <si>
+    <t>The Ninja Life Hacks Emotions and Feelings Box Set includes books 1-8:Angry NinjaPositive NinjaEarth NinjaInventor NinjaGrumpy NinjaHelpful NinjaKind NinjaLazy NinjaLife is hard. It’s even harder for children who are just trying to figure things out.The new social-emotional learning children's book series, Ninja Life Hacks, was developed to help children learn valuable life skills. Fun, pint-size characters in comedic books easy enough for young readers, yet witty enough for adults.The Ninja Life Hacks book series is geared to kids 4-10+. Perfect for boys, girls, early readers, primary school students, or toddlers.  Excellent resource for educators, parents, and teachers alike.Collect all the Ninja Life Hacks Book Sets.Ninja Life Hacks Emotions and Feelings Box SetNinja Life Hacks Growth Mindset Box SetNinja Life Hacks Leadership Box SetNinja Life Hacks Mover and Shaker Box SetNinja Life Hacks Self Management Box SetNinja Life Hacks Self Awareness Box SetNinja Life Hacks Decision Making Box SetNinja Life Hacks Social Awareness and Relationship Skills Box SetNinja Life Hacks Mindsets Box SetNinja Life Hacks Behaviors Box SetNinja Life Hacks Ninjas Go! Box SetNinjas on Holiday Box SetEmotions and Feelings Toy Box SetMakes a perfect gift! (No books in our sets overlap.)  Read more</t>
+  </si>
+  <si>
+    <t>9781959284048</t>
+  </si>
+  <si>
+    <t>My Superpower Values 8 Book Box Set (Books 1-8: Kindness, Mindfulness, Acceptance, Gratitude, Confidence, Honesty, Patience, and Love) (My Superpower Books)</t>
+  </si>
+  <si>
+    <t>Slickcolors Inc</t>
+  </si>
+  <si>
+    <t>3.26</t>
+  </si>
+  <si>
+    <t>8.58</t>
+  </si>
+  <si>
+    <t>1.57</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71wbH4qikFL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781959284048.jpg</t>
+  </si>
+  <si>
+    <t>My Superpower Values includes books 1-8:Kindness is My SuperpowerBreathing is My SuperpowerAcceptance is My SuperpowerGratitude is My SuperpowerConfidence is My SuperpowerHonesty is My SuperpowerPatience is My SuperpowerLove is My SuperpowerMy Superpower Values was developed to teach children about emotions, values, and the superpower behind learning how to manage them from an early age.The box set is perfect for children 3-8 and is suitable for boys, girls, early readers, primary school students, and even toddlers. It serves as an exceptional resource for educators, parents, and teachers.  Read more</t>
+  </si>
+  <si>
+    <t>9781426220586</t>
+  </si>
+  <si>
+    <t>National Geographic Atlas of the World, 11th Edition</t>
+  </si>
+  <si>
+    <t>National Geographic</t>
+  </si>
+  <si>
+    <t>12.6</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>18.9</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81OPXP13-ZL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781426220586.jpg</t>
+  </si>
+  <si>
+    <t>Every corner of the world revealed in this ultimate atlas, created by the world's premier cartographic publisher.More than 300 maps and graphics represent every state, province, country, territory, and island, plus the poles, oceans, planets, and beyond.Elegant and authoritative, packaged in a protective slipcase box, National Geographic's 11th edition of its flagship Atlas of the World provides precise, detailed, easy-to-read maps of all regions of the world.Organized by continent and reflecting current boundaries and identities, this top-of-the-line atlas offers hours of browsing fascination for the globally inquisitive.20 broad-ranging thematic spreads open the book, including maps and data-rich graphics on topics from tectonics and climate to world economy and energy sources.A special section on Space includes star charts, maps of the Moon and Mars, depictions of the Milky Way and the larger universe, and a custom visualization of all human space explorations.Additional features include:Flags, key data, and brief descriptions of all 195 countriesAn intriguing array of geographical details, from the age and mass of the planet to engineering wonders and population extremesNavigational endsheets with a world map sectioned off and keyed to every map insideHigh-quality paper and printing, bookmark ribbon, protective slipcaseA comprehensive index citing more than 150,000 locations found on the maps withinThis glorious large-format atlas doubles as a gorgeous coffee table keepsake and an endless learning experience for the curious-minded: students, travelers, explorers both armchair and otherwise, and every family library seeking the finest in cartographic excellence and enjoyment.  Read more</t>
+  </si>
+  <si>
+    <t>9780590431620</t>
+  </si>
+  <si>
+    <t>This Is the Way We Go to School: A Book About Children Around the World</t>
+  </si>
+  <si>
+    <t>Scholastic</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81-WMGgoH7L._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9780590431620.jpg</t>
+  </si>
+  <si>
+    <t>Enthusiastic children around the world are on their way to school. But how do they get there? The answers are as varied as the landscapes, which range from Egypt's sandy desert to Switzerland's snowy peaks. Jaunty rhymes ― in Venice, "Bianca, Beppo, Benedetto, ride aboard the vaporetto" ― and exuberant watercolors celebrate the individuality of each locale, and there are plenty of humorous details to please eagle-eyed readers as they join their fellow students to travel by ferry, trolley car, helicopter, and more. A world map is included at the end, along with a summary listing where all the children in the story live.Sure to awaken student curiosity about the world, This Is the Way We Go to School combines themes of transportation, school, culture, and childhood into a not-to-be-missed multicultural extravaganza.  Read more</t>
+  </si>
+  <si>
+    <t>9781788950787</t>
+  </si>
+  <si>
+    <t>Little Penguin Rescue (Little Animal Rescue)</t>
+  </si>
+  <si>
+    <t>Stripes Publishing</t>
+  </si>
+  <si>
+    <t>5.08</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71aGH4tK9ML._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9781788950787.jpg</t>
+  </si>
+  <si>
+    <t>Fliss loves animals and will do anything to save them! Join her on her adventures to save wild animals in danger.  In the middle of a snowball fight, aspiring vet Fliss is whisked away to the Antarctic! Surrounded by penguins, Fliss marvels at the sight of these beautiful animals huddling together to keep warm. Then a snowstorm blows in, separating a chick and its injured mother from the group. Fliss is determined to return her feathery friends to their colony, but the icy waters are full of dangerous creatures and Fliss isn’t used to the harsh environment. It’s going to take a lot of quick thinking, and waddling, to reunite them…  LITTLE PENGUIN RESCUE is perfect for fans of Holly Webb, the ZOE’S RESCUE ZOO series, and animal-lovers everywhere!  Read more</t>
+  </si>
+  <si>
+    <t>9780545639149</t>
+  </si>
+  <si>
+    <t>Rescue on the Oregon Trail (Ranger in Time #1) (1)</t>
+  </si>
+  <si>
+    <t>Scholastic Press</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>7.75</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81bvjMpGhML._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>9780545639149.jpg</t>
+  </si>
+  <si>
+    <t>Meet Ranger! He's a time-traveling golden retriever who has a nose for trouble . . . and always saves the day!Ranger has been trained as a search-and-rescue dog, but can't officially pass the test because he's always getting distracted by squirrels during exercises. One day, he finds a mysterious first aid kit in the garden and is transported to the year 1850, where he meets a young boy named Sam Abbott. Sam's family is migrating west on the Oregon Trail, and soon after Ranger arrives he helps the boy save his little sister. Ranger thinks his job is done, but the Oregon Trail can be dangerous, and the Abbotts need Ranger's help more than they realize!  Read more</t>
+  </si>
+  <si>
+    <t>9781107549876</t>
+  </si>
+  <si>
+    <t>Cambridge Reading Adventures The Sun is Up Pink A Band</t>
+  </si>
+  <si>
+    <t>Cambridge University Press</t>
+  </si>
+  <si>
+    <t>New Edition</t>
+  </si>
+  <si>
+    <t>2.19</t>
+  </si>
+  <si>
+    <t>7.23</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>9.25</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51tqulH-ZzL.jpg</t>
+  </si>
+  <si>
+    <t>9781107549876.jpg</t>
+  </si>
+  <si>
+    <t>Our international primary reading series will help your learners become confident, independent readers. The sun is up, what is it shining on? Pink A books are intended for new readers with around 30-60 words, colourful illustrations and a high level of repetition to help with word recognition. Contains full teaching support including learning outcomes, curriculum links and follow-up activities.  Read more</t>
   </si>
 </sst>
 </file>
@@ -398,8 +1145,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -442,6 +1192,1195 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L7" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" t="s">
+        <v>95</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11" t="s">
+        <v>102</v>
+      </c>
+      <c r="J11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L11" t="s">
+        <v>104</v>
+      </c>
+      <c r="M11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H12" t="s">
+        <v>111</v>
+      </c>
+      <c r="I12" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>113</v>
+      </c>
+      <c r="L12" t="s">
+        <v>114</v>
+      </c>
+      <c r="M12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L13" t="s">
+        <v>124</v>
+      </c>
+      <c r="M13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" t="s">
+        <v>56</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" t="s">
+        <v>129</v>
+      </c>
+      <c r="L14" t="s">
+        <v>130</v>
+      </c>
+      <c r="M14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" t="s">
+        <v>134</v>
+      </c>
+      <c r="I15" t="s">
+        <v>135</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" t="s">
+        <v>136</v>
+      </c>
+      <c r="L15" t="s">
+        <v>137</v>
+      </c>
+      <c r="M15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" t="s">
+        <v>121</v>
+      </c>
+      <c r="I16" t="s">
+        <v>135</v>
+      </c>
+      <c r="J16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" t="s">
+        <v>142</v>
+      </c>
+      <c r="L16" t="s">
+        <v>143</v>
+      </c>
+      <c r="M16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" t="s">
+        <v>135</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L17" t="s">
+        <v>148</v>
+      </c>
+      <c r="M17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" t="s">
+        <v>155</v>
+      </c>
+      <c r="I18" t="s">
+        <v>156</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" t="s">
+        <v>157</v>
+      </c>
+      <c r="L18" t="s">
+        <v>158</v>
+      </c>
+      <c r="M18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" t="s">
+        <v>162</v>
+      </c>
+      <c r="D19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
+        <v>164</v>
+      </c>
+      <c r="H19" t="s">
+        <v>165</v>
+      </c>
+      <c r="I19" t="s">
+        <v>166</v>
+      </c>
+      <c r="J19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" t="s">
+        <v>167</v>
+      </c>
+      <c r="L19" t="s">
+        <v>168</v>
+      </c>
+      <c r="M19" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" t="s">
+        <v>173</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
+        <v>174</v>
+      </c>
+      <c r="H20" t="s">
+        <v>175</v>
+      </c>
+      <c r="I20" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" t="s">
+        <v>177</v>
+      </c>
+      <c r="L20" t="s">
+        <v>178</v>
+      </c>
+      <c r="M20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>183</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" t="s">
+        <v>185</v>
+      </c>
+      <c r="I21" t="s">
+        <v>186</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>187</v>
+      </c>
+      <c r="L21" t="s">
+        <v>188</v>
+      </c>
+      <c r="M21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" t="s">
+        <v>191</v>
+      </c>
+      <c r="C22" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" t="s">
+        <v>193</v>
+      </c>
+      <c r="L22" t="s">
+        <v>194</v>
+      </c>
+      <c r="M22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>196</v>
+      </c>
+      <c r="B23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C23" t="s">
+        <v>198</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" t="s">
+        <v>199</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" t="s">
+        <v>200</v>
+      </c>
+      <c r="I23" t="s">
+        <v>102</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" t="s">
+        <v>201</v>
+      </c>
+      <c r="L23" t="s">
+        <v>202</v>
+      </c>
+      <c r="M23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>204</v>
+      </c>
+      <c r="B24" t="s">
+        <v>205</v>
+      </c>
+      <c r="C24" t="s">
+        <v>206</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" t="s">
+        <v>207</v>
+      </c>
+      <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" t="s">
+        <v>208</v>
+      </c>
+      <c r="L24" t="s">
+        <v>209</v>
+      </c>
+      <c r="M24" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>211</v>
+      </c>
+      <c r="B25" t="s">
+        <v>212</v>
+      </c>
+      <c r="C25" t="s">
+        <v>213</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" t="s">
+        <v>214</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" t="s">
+        <v>215</v>
+      </c>
+      <c r="H25" t="s">
+        <v>215</v>
+      </c>
+      <c r="I25" t="s">
+        <v>216</v>
+      </c>
+      <c r="J25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" t="s">
+        <v>217</v>
+      </c>
+      <c r="L25" t="s">
+        <v>218</v>
+      </c>
+      <c r="M25" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>220</v>
+      </c>
+      <c r="B26" t="s">
+        <v>221</v>
+      </c>
+      <c r="C26" t="s">
+        <v>222</v>
+      </c>
+      <c r="D26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" t="s">
+        <v>141</v>
+      </c>
+      <c r="F26" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" t="s">
+        <v>223</v>
+      </c>
+      <c r="H26" t="s">
+        <v>224</v>
+      </c>
+      <c r="I26" t="s">
+        <v>225</v>
+      </c>
+      <c r="J26" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s">
+        <v>226</v>
+      </c>
+      <c r="L26" t="s">
+        <v>227</v>
+      </c>
+      <c r="M26" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>229</v>
+      </c>
+      <c r="B27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C27" t="s">
+        <v>231</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>232</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H27" t="s">
+        <v>40</v>
+      </c>
+      <c r="I27" t="s">
+        <v>110</v>
+      </c>
+      <c r="J27" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" t="s">
+        <v>233</v>
+      </c>
+      <c r="L27" t="s">
+        <v>234</v>
+      </c>
+      <c r="M27" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>236</v>
+      </c>
+      <c r="B28" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" t="s">
+        <v>238</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" t="s">
+        <v>239</v>
+      </c>
+      <c r="J28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K28" t="s">
+        <v>240</v>
+      </c>
+      <c r="L28" t="s">
+        <v>241</v>
+      </c>
+      <c r="M28" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>243</v>
+      </c>
+      <c r="B29" t="s">
+        <v>244</v>
+      </c>
+      <c r="C29" t="s">
+        <v>245</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H29" t="s">
+        <v>94</v>
+      </c>
+      <c r="I29" t="s">
+        <v>247</v>
+      </c>
+      <c r="J29" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" t="s">
+        <v>248</v>
+      </c>
+      <c r="L29" t="s">
+        <v>249</v>
+      </c>
+      <c r="M29" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B30" t="s">
+        <v>252</v>
+      </c>
+      <c r="C30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D30" t="s">
+        <v>254</v>
+      </c>
+      <c r="E30" t="s">
+        <v>255</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>256</v>
+      </c>
+      <c r="H30" t="s">
+        <v>257</v>
+      </c>
+      <c r="I30" t="s">
+        <v>258</v>
+      </c>
+      <c r="J30" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" t="s">
+        <v>259</v>
+      </c>
+      <c r="L30" t="s">
+        <v>260</v>
+      </c>
+      <c r="M30" t="s">
+        <v>261</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output.xlsx
+++ b/output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,55 +429,85 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Tác giả</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Năm xuất bản</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>NXB</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Kích thước</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Khối lượng</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Đơn vị khối lượng</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Dài (Length)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Rộng (Width)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Cao (Height)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Đơn vị kích thước</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Số trang</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Khối lượng</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Đơn vị khối lượng</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dài (Length)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Rộng (Width)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Cao (Height)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Đơn vị kích thước</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>image_url</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>image_name</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>description(vi)</t>
         </is>
@@ -486,203 +516,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9781444939453</t>
+          <t>9781789894547</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Toto Ninja Cat &amp; Great Snake Escape</t>
+          <t>Wonderful Words: Bugs!</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hodder Children's Books</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Paperback</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ounces</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>7.76</t>
-        </is>
-      </c>
+          <t>Amy Johnson</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>inches</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/91QwpOHcvVL._SY522_.jpg</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>9781444939453.jpg</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Meet Toto: she's no ordinary cat, and she can't wait to have an adventure with you!Toto the cat and her brother Silver live footloose and fancy-free in a townhouse in London. Toto is almost totally blind, and learned to trust her senses from a ninja cat-master who taught her back in Italy where they were born. By day, Toto and Silver seem to be ordinary cats, but by night, they love to have adventures!One evening, news reaches Toto that a king cobra has escaped from London Zoo! Together with help from a very posh cat and two hungry tigers, Toto and Silver must investigate. Can they find the giant snake, before it's too late?  Read more</t>
-        </is>
-      </c>
+          <t>pounds</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Hardcover</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81gcHKhZrlL._SY522_.jpg</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>9781789894547.jpg</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9780316381251</t>
+          <t>9781444939453</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>Toto Ninja Cat &amp; Great Snake Escape</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>University of Chicago Press</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hardcover</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
+          <t>Dermot O'Leary</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pounds</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>Hodder Children's Books</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>ounces</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>7.76</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>inches</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81R4opASwAL._SY522_.jpg</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>9780316381251.jpg</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>The greatest of all epics, soon to be a film by Christopher Nolan!“This may be the best translation of The Odyssey yet."—Edith Hall, The TelegraphA magnificent feat of translation, hailed by classicists and poets alike as a “momentous achievement”: “thrilling,” “rich and rhythmical,” “superb,” “mesmerizing,” “searingly faithful—yet absolutely original.”   With this edition of Homer’s Odyssey, the celebrated author, critic, and classicist Daniel Mendelsohn brings the great epic to vividly poetic new life. Widely known for his essays on classical literature and culture in The New Yorker and many other publications, Mendelsohn gives us a line-for-line rendering of The Odyssey that is both engrossing as poetry and true to its source. Rejecting the streamlining and modernizing approach of many recent translations, he artfully reproduces the epic’s formal qualities—meter, enjambment, alliteration, assonance—and in so doing restores to Homer’s masterwork its archaic grandeur. Mendelsohn’s expansive six-beat line, far closer to the original than that of other recent translations, allows him to capture each of Homer’s dense verses without sacrificing the amplitude and shadings of the original. The result is the richest, most ample, most precise, and most musical Odyssey in English, conveying the beauty of its poetry, the excitement of its hero’s adventures, and the profundity of its insights. Supported by an extensive introduction and the fullest notes and commentary currently available, Daniel Mendelsohn’s Odyssey is poised to become the authoritative version of this magnificent and enduringly influential masterpiece.  Read more</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Paperback</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/91QwpOHcvVL._SY522_.jpg</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>9781444939453.jpg</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9798339702337</t>
+          <t>9780316381251</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Events by Kids</t>
+          <t>The Iliad: Deluxe Edition Featuring The Achilleid and Original Illustrations (Illustrated)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Everlasting Classics</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Independently published</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>pounds</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inches</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>Paperback</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ounces</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>inches</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/713xaF-7G5L._SY522_.jpg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>9798339702337.jpg</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Kid’s events shouldn’t be done by adults—they should be done by kids! "Events by Kids" is an ultimate guide that will empower children to imagine, plan, organize, lead, collaborate, and communicate by planning their own events. This book takes young readers through every step of event planning, from birthday parties to talent shows, making it fun and easy to create unforgettable experiences. With inspiring ideas, hands-on activities, and vibrant examples, this book is perfect for kids who want to take charge and bring their creative visions to life.This book is part of the global project, which includes an online educational course, a series of instructional books, face-to-face activities, and exclusive services for parents. The project’s mission is to empower children by teaching them how to organize and manage their own events, fostering creativity, responsibility, and practical skills that will benefit them throughout their lives. Turn every child into an event-planning superstar with "Events by Kids!”  Read more</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71DynbJRTfL._SY522_.jpg</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>9780316381251.jpg</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
